--- a/study_case_model/scenario_variables/compare_models/smaller_network/price_scenarios144.xlsx
+++ b/study_case_model/scenario_variables/compare_models/smaller_network/price_scenarios144.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,22 +417,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>stage</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>scenario_index</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>node</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
@@ -463,7 +451,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>30.04931005500636</v>
+        <v>34.1059136340686</v>
       </c>
     </row>
     <row r="3">
@@ -479,7 +467,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>22.66793131208874</v>
+        <v>26.27884633185299</v>
       </c>
     </row>
     <row r="4">
@@ -495,7 +483,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>19.05099152759472</v>
+        <v>24.43953796601825</v>
       </c>
     </row>
     <row r="5">
@@ -511,7 +499,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>30.32730130653706</v>
+        <v>34.02770831483262</v>
       </c>
     </row>
     <row r="6">
@@ -527,7 +515,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>22.50681380568967</v>
+        <v>26.95208782737049</v>
       </c>
     </row>
     <row r="7">
@@ -543,7 +531,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>19.21660284052831</v>
+        <v>24.54773009197186</v>
       </c>
     </row>
     <row r="8">
@@ -559,7 +547,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>30.03199033670014</v>
+        <v>34.10402436805959</v>
       </c>
     </row>
     <row r="9">
@@ -575,7 +563,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>23.06222324339579</v>
+        <v>26.66826415858548</v>
       </c>
     </row>
     <row r="10">
@@ -591,7 +579,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>19.27021915730926</v>
+        <v>24.36180213056284</v>
       </c>
     </row>
     <row r="11">
@@ -607,7 +595,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>29.89421415597641</v>
+        <v>33.95355566215715</v>
       </c>
     </row>
     <row r="12">
@@ -623,7 +611,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>22.82906264028827</v>
+        <v>26.70021120721777</v>
       </c>
     </row>
     <row r="13">
@@ -639,7 +627,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>19.03752944852597</v>
+        <v>24.2314655998787</v>
       </c>
     </row>
     <row r="14">
@@ -655,7 +643,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>27.89940202811942</v>
+        <v>31.45185159291432</v>
       </c>
     </row>
     <row r="15">
@@ -671,7 +659,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>24.67094004521482</v>
+        <v>28.11255755036373</v>
       </c>
     </row>
     <row r="16">
@@ -687,7 +675,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>26.86395844640877</v>
+        <v>25.72598047953278</v>
       </c>
     </row>
     <row r="17">
@@ -703,7 +691,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>27.89606042109188</v>
+        <v>31.65213994154238</v>
       </c>
     </row>
     <row r="18">
@@ -719,7 +707,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>25.34990113132303</v>
+        <v>27.4537119582742</v>
       </c>
     </row>
     <row r="19">
@@ -735,7 +723,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>27.27222057921592</v>
+        <v>25.73796383025632</v>
       </c>
     </row>
     <row r="20">
@@ -751,7 +739,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>27.80905385925007</v>
+        <v>31.9076886707305</v>
       </c>
     </row>
     <row r="21">
@@ -767,7 +755,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>25.08830290971215</v>
+        <v>28.10298775282493</v>
       </c>
     </row>
     <row r="22">
@@ -783,7 +771,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>26.82302863755143</v>
+        <v>25.56987530996486</v>
       </c>
     </row>
     <row r="23">
@@ -799,7 +787,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>27.64083815019331</v>
+        <v>32.05266470513598</v>
       </c>
     </row>
     <row r="24">
@@ -815,7 +803,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>25.04815738710377</v>
+        <v>28.54891668579655</v>
       </c>
     </row>
     <row r="25">
@@ -831,7 +819,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>27.51337209169133</v>
+        <v>25.52394950383831</v>
       </c>
     </row>
     <row r="26">
@@ -847,7 +835,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>26.91349196908346</v>
+        <v>34.2505689504073</v>
       </c>
     </row>
     <row r="27">
@@ -863,7 +851,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>23.62161694059622</v>
+        <v>24.70320022431941</v>
       </c>
     </row>
     <row r="28">
@@ -879,7 +867,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>31.81881676839676</v>
+        <v>25.65857723298186</v>
       </c>
     </row>
     <row r="29">
@@ -895,7 +883,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>26.71804479194902</v>
+        <v>33.90188166244841</v>
       </c>
     </row>
     <row r="30">
@@ -911,7 +899,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>23.88278002067884</v>
+        <v>23.91366246508097</v>
       </c>
     </row>
     <row r="31">
@@ -927,7 +915,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>31.91002963528169</v>
+        <v>26.02350008161933</v>
       </c>
     </row>
     <row r="32">
@@ -943,7 +931,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>27.09785675089455</v>
+        <v>33.68792692391575</v>
       </c>
     </row>
     <row r="33">
@@ -959,7 +947,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>24.2694810595559</v>
+        <v>24.43022220367711</v>
       </c>
     </row>
     <row r="34">
@@ -975,7 +963,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>31.44986371569519</v>
+        <v>25.29685280265736</v>
       </c>
     </row>
     <row r="35">
@@ -991,7 +979,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>26.73839410864712</v>
+        <v>34.37822840404226</v>
       </c>
     </row>
     <row r="36">
@@ -1007,7 +995,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>24.12520374908611</v>
+        <v>24.51117898344141</v>
       </c>
     </row>
     <row r="37">
@@ -1023,7 +1011,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>32.02543438591506</v>
+        <v>24.98335597984618</v>
       </c>
     </row>
     <row r="38">
@@ -1039,7 +1027,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>28.69579500590828</v>
+        <v>28.04771246785457</v>
       </c>
     </row>
     <row r="39">
@@ -1055,7 +1043,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>28.13674341757373</v>
+        <v>23.85489832884909</v>
       </c>
     </row>
     <row r="40">
@@ -1071,7 +1059,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>20.21730868168078</v>
+        <v>22.82760723908265</v>
       </c>
     </row>
     <row r="41">
@@ -1087,7 +1075,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>28.48904617509389</v>
+        <v>28.6686957033156</v>
       </c>
     </row>
     <row r="42">
@@ -1103,7 +1091,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>28.41812251887793</v>
+        <v>23.33190651103266</v>
       </c>
     </row>
     <row r="43">
@@ -1119,7 +1107,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>20.72074476088565</v>
+        <v>22.52124850667338</v>
       </c>
     </row>
     <row r="44">
@@ -1135,7 +1123,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>28.81319654397454</v>
+        <v>28.03753229109764</v>
       </c>
     </row>
     <row r="45">
@@ -1151,7 +1139,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>28.47196565423427</v>
+        <v>23.59819176258044</v>
       </c>
     </row>
     <row r="46">
@@ -1167,7 +1155,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>20.51741306972042</v>
+        <v>22.48196752896152</v>
       </c>
     </row>
     <row r="47">
@@ -1183,7 +1171,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>28.64794634212739</v>
+        <v>27.94575591978797</v>
       </c>
     </row>
     <row r="48">
@@ -1199,7 +1187,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>28.29095306576836</v>
+        <v>23.433425534988</v>
       </c>
     </row>
     <row r="49">
@@ -1215,7 +1203,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>20.75791030352098</v>
+        <v>22.6444987223734</v>
       </c>
     </row>
   </sheetData>
